--- a/Day 3/Datasets/credit_card_transactions.xlsx
+++ b/Day 3/Datasets/credit_card_transactions.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academics\MDPs\May 2026\Day 3\Datasets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Academics\MDPs\5-Day Online Hands-on Workshop (MDP) on AIML\Day 3\Datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD094A4-EF8D-40FB-A691-418BA1F60671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
